--- a/Excel/Employee Capstone Project/Employee Captsone Project.xlsx
+++ b/Excel/Employee Capstone Project/Employee Captsone Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DATA ANALYTICS\Capstone Projects\Data-Analysis-Projects\Excel\Employee Capstone Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DD26C6-9AC9-4CB7-8B7A-3066973A428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29CDCB0A-7E1C-4647-870C-92006A007F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="738" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="738" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Possible Analysis Questions" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9054" uniqueCount="2005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9064" uniqueCount="2006">
   <si>
     <t>EEID</t>
   </si>
@@ -6092,14 +6092,18 @@
   <si>
     <t>Column Labels</t>
   </si>
+  <si>
+    <t>Average of Age</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;GH₵&quot;* #,##0.00_-;\-&quot;GH₵&quot;* #,##0.00_-;_-&quot;GH₵&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -6160,7 +6164,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -6178,12 +6182,49 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="30">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
@@ -6252,820 +6293,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[Employee Captsone Project.xlsx]Pivot!PivotTable3</c:name>
-    <c:fmtId val="4"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-GH"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-GH"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Pivot!$B$10</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Pivot!$A$11:$A$18</c:f>
-              <c:strCache>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>Accounting</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Engineering</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Finance</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Human Resources</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>IT</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Marketing</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Sales</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Pivot!$B$11:$B$18</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>158</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>120</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>125</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>241</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>120</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>140</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FDAC-4AF8-B93E-79D98774150B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="188272895"/>
-        <c:axId val="188272415"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="188272895"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-GH"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="188272415"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="188272415"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-GH"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="188272895"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-GH"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-GH"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[Employee Captsone Project.xlsx]Pivot!PivotTable4</c:name>
-    <c:fmtId val="14"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-GH"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-GH"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Pivot!$B$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Pivot!$A$22:$A$25</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Brazil</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>China</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>United States</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Pivot!$B$22:$B$25</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>139</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>218</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>643</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A7F5-404C-9ADC-270D9DAA0EFB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="1040748319"/>
-        <c:axId val="1040755999"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1040748319"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-GH"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1040755999"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1040755999"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-GH"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1040748319"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-GH"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-GH"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7565,7 +6792,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8038,6 +7265,508 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Employee Captsone Project.xlsx]Pivot!PivotTable5</c:name>
+    <c:fmtId val="32"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1200"/>
+              <a:t>Average</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1200" baseline="0"/>
+              <a:t> age by department</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1200"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-GH"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="lt1"/>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="F0A22E">
+                <a:alpha val="70000"/>
+              </a:srgbClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-GH"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pivot!$E$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
+                <a:schemeClr val="accent1"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="lt1"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="F0A22E">
+                  <a:alpha val="70000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-GH"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="60000"/>
+                          <a:lumOff val="40000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pivot!$D$7:$D$14</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Accounting</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Engineering</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Human Resources</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pivot!$E$7:$E$14</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>43.65625</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45.670886075949369</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45.291666666666664</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44.456000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44.344398340248965</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>43.216666666666669</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>43.642857142857146</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-89EF-41A8-92E0-F0551C9AD314}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="269"/>
+        <c:overlap val="-20"/>
+        <c:axId val="1130776703"/>
+        <c:axId val="1130773343"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1130776703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-GH"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1130773343"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1130773343"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-GH"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1130776703"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-GH"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -8158,100 +7887,57 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="226">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="bg1"/>
+        <a:schemeClr val="phClr"/>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -8260,25 +7946,30 @@
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <cs:styleClr val="auto"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -8286,10 +7977,7 @@
       </a:solidFill>
       <a:ln>
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
@@ -8300,58 +7988,87 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
@@ -8360,10 +8077,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -8375,90 +8092,97 @@
     </cs:spPr>
   </cs:dataPointWireframe>
   <cs:dataTable>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:errorBar>
   <cs:floor>
@@ -8466,28 +8190,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8495,59 +8214,62 @@
     </cs:spPr>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
   <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
   <cs:leaderLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -8556,57 +8278,67 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -8615,28 +8347,25 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
+    <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -8645,32 +8374,32 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -8679,10 +8408,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
@@ -8691,72 +8417,63 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="226">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="bg1"/>
+        <a:schemeClr val="phClr"/>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -8765,25 +8482,30 @@
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <cs:styleClr val="auto"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -8791,10 +8513,7 @@
       </a:solidFill>
       <a:ln>
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
@@ -8805,58 +8524,87 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
@@ -8865,10 +8613,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -8880,90 +8628,97 @@
     </cs:spPr>
   </cs:dataPointWireframe>
   <cs:dataTable>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:errorBar>
   <cs:floor>
@@ -8971,28 +8726,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9000,59 +8750,62 @@
     </cs:spPr>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
   <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
   <cs:leaderLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -9061,57 +8814,67 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -9120,28 +8883,25 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
+    <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -9150,32 +8910,32 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -9184,10 +8944,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
@@ -9196,14 +8953,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -9744,620 +9495,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="226">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="800" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="70000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <cs:styleClr val="auto"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="ltUpDiag">
-        <a:fgClr>
-          <a:schemeClr val="phClr"/>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="lt1"/>
-        </a:bgClr>
-      </a:pattFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="ltUpDiag">
-        <a:fgClr>
-          <a:schemeClr val="phClr"/>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="lt1"/>
-        </a:bgClr>
-      </a:pattFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:effectRef>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-      <a:effectLst>
-        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
-          <a:schemeClr val="phClr"/>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="22225">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="35000"/>
-          <a:lumOff val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-      <a:effectLst>
-        <a:glow rad="25400">
-          <a:schemeClr val="lt1"/>
-        </a:glow>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-            <a:tint val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="0"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="95000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>34925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>736600</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>15875</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B6DD397-CCE8-EB0A-6474-2DA97FFE7890}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41264335-18EE-F1E6-88B5-32BF3BD1417B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -10869,9 +10007,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>550334</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>162277</xdr:rowOff>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>141111</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10887,7 +10025,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="247650" y="999771"/>
-          <a:ext cx="4013906" cy="8885062"/>
+          <a:ext cx="4035072" cy="7212896"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -11021,8 +10159,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>349250</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>155222</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>169334</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11052,15 +10190,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>331611</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>176388</xdr:rowOff>
+      <xdr:colOff>359833</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>98777</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>310445</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>119944</xdr:rowOff>
+      <xdr:colOff>338667</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11082,6 +10220,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>395112</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>148166</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>388056</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>91721</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="21" name="Chart 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66FFA64E-FA86-4A39-B5E8-99AFC6D9FE25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -27168,6 +26344,137 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{608404ED-3248-4EA1-B5D5-DF5676A338DF}" name="PivotTable5" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="35">
+  <location ref="D6:E14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Age" fld="7" subtotal="average" baseField="3" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="11">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="30" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3CAE2DA7-A0C2-401E-843D-03536A65EC6B}" name="PivotTable4" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
   <location ref="A21:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -27234,11 +26541,11 @@
     <dataField name="Count of Full Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="16">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="5">
+  <chartFormats count="4">
     <chartFormat chart="4" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -27258,15 +26565,6 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="14" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="15" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -27297,7 +26595,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C7E16241-B645-485F-B228-1C03EBDCF124}" name="PivotTable3" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
   <location ref="A10:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -27369,7 +26667,7 @@
     <dataField name="Count of Full Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="5">
+    <format dxfId="17">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -27405,7 +26703,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B28366B1-6149-48E9-BD88-17573D122A1A}" name="PivotTable1" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:D3" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="14">
@@ -27462,7 +26760,7 @@
     <dataField name="Count of Full Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="6">
+    <format dxfId="18">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -27505,20 +26803,20 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{810CE1A3-8C28-4A4E-86B2-0687B259217E}" name="emp" displayName="emp" ref="A1:N1001" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:N1001" xr:uid="{810CE1A3-8C28-4A4E-86B2-0687B259217E}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{6E34069D-4199-4D94-A78E-19E6451E4B1D}" uniqueName="1" name="EEID" queryTableFieldId="1" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{9E44F958-27FD-4283-B406-E4E278FD01CD}" uniqueName="2" name="Full Name" queryTableFieldId="2" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{A28550E9-1F62-45ED-8EE5-9C5E4946FDED}" uniqueName="3" name="Job Title" queryTableFieldId="3" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{E77DFBE1-0E2C-43CC-92C2-73C5FE73C7B1}" uniqueName="4" name="Department" queryTableFieldId="4" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{51040676-C726-45D8-B30D-745E4BA3352D}" uniqueName="5" name="Business Unit" queryTableFieldId="5" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{0AA061D1-F6AF-473C-A5A2-7440DC296B56}" uniqueName="6" name="Gender" queryTableFieldId="6" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{944E53E6-AF72-4759-AB4E-3DEDD74E22B0}" uniqueName="7" name="Ethnicity" queryTableFieldId="7" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{6E34069D-4199-4D94-A78E-19E6451E4B1D}" uniqueName="1" name="EEID" queryTableFieldId="1" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{9E44F958-27FD-4283-B406-E4E278FD01CD}" uniqueName="2" name="Full Name" queryTableFieldId="2" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{A28550E9-1F62-45ED-8EE5-9C5E4946FDED}" uniqueName="3" name="Job Title" queryTableFieldId="3" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{E77DFBE1-0E2C-43CC-92C2-73C5FE73C7B1}" uniqueName="4" name="Department" queryTableFieldId="4" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{51040676-C726-45D8-B30D-745E4BA3352D}" uniqueName="5" name="Business Unit" queryTableFieldId="5" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{0AA061D1-F6AF-473C-A5A2-7440DC296B56}" uniqueName="6" name="Gender" queryTableFieldId="6" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{944E53E6-AF72-4759-AB4E-3DEDD74E22B0}" uniqueName="7" name="Ethnicity" queryTableFieldId="7" dataDxfId="23"/>
     <tableColumn id="8" xr3:uid="{B77A9822-3394-494B-B792-48CC6128F3C4}" uniqueName="8" name="Age" queryTableFieldId="8"/>
-    <tableColumn id="9" xr3:uid="{0C3C40F0-43BB-4C5E-8998-81896A46A673}" uniqueName="9" name="Hire Date" queryTableFieldId="9" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{0C3C40F0-43BB-4C5E-8998-81896A46A673}" uniqueName="9" name="Hire Date" queryTableFieldId="9" dataDxfId="22"/>
     <tableColumn id="10" xr3:uid="{97596652-FB9C-4FA0-B94B-39FDE7650C71}" uniqueName="10" name="Annual Salary" queryTableFieldId="10" dataCellStyle="Currency"/>
     <tableColumn id="11" xr3:uid="{E088A45F-0A5A-40D3-8F65-F023A43E7403}" uniqueName="11" name="Bonus %" queryTableFieldId="11"/>
-    <tableColumn id="12" xr3:uid="{44CCE0B0-2AD3-474D-A378-6CAABFC23D5E}" uniqueName="12" name="Country" queryTableFieldId="12" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{CB5EA8BC-00A2-488A-B8BB-BD2B2369C228}" uniqueName="13" name="City" queryTableFieldId="13" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{209469EA-D90D-46C8-9AF0-28C78CDD7020}" uniqueName="14" name="Exit Date" queryTableFieldId="14" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{44CCE0B0-2AD3-474D-A378-6CAABFC23D5E}" uniqueName="12" name="Country" queryTableFieldId="12" dataDxfId="21"/>
+    <tableColumn id="13" xr3:uid="{CB5EA8BC-00A2-488A-B8BB-BD2B2369C228}" uniqueName="13" name="City" queryTableFieldId="13" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{209469EA-D90D-46C8-9AF0-28C78CDD7020}" uniqueName="14" name="Exit Date" queryTableFieldId="14" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -70168,26 +69466,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD4D3BB7-7CA9-40A0-A2DA-216B712B213B}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B1" s="7" t="s">
         <v>2004</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>19</v>
       </c>
@@ -70198,7 +69496,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2003</v>
       </c>
@@ -70212,47 +69510,109 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D6" s="7" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="11">
+        <v>43.65625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="11">
+        <v>45.670886075949369</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="11">
+        <v>45.291666666666664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>2001</v>
       </c>
       <c r="B10" t="s">
         <v>2003</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D10" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="11">
+        <v>44.456000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B11" s="9">
         <v>96</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="11">
+        <v>44.344398340248965</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>69</v>
       </c>
       <c r="B12" s="9">
         <v>158</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D12" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="11">
+        <v>43.216666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="9">
         <v>120</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="11">
+        <v>43.642857142857146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B14" s="9">
         <v>125</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D14" s="8" t="s">
+        <v>2002</v>
+      </c>
+      <c r="E14" s="10">
+        <v>44.381999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>17</v>
       </c>
@@ -70260,7 +69620,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>80</v>
       </c>
@@ -70326,7 +69686,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
